--- a/Test upload format/Mudra/IA/2026 - 2027/CP3 26-27.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027/CP3 26-27.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="9600"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="34">
   <si>
     <t>custid</t>
   </si>
@@ -74,46 +74,61 @@
     <t>pan</t>
   </si>
   <si>
-    <t>SVR21014</t>
-  </si>
-  <si>
-    <t>3000</t>
+    <t>taruncategoryearlier</t>
+  </si>
+  <si>
+    <t>accountsrepaidsatisfactorily</t>
+  </si>
+  <si>
+    <t>AnyLoansInNPASuitFiledSettledOTS</t>
+  </si>
+  <si>
+    <t>modifiedloancat</t>
+  </si>
+  <si>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>2627CR701</t>
+  </si>
+  <si>
+    <t>2627CR703</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>01-04-2026</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>1997000</t>
-  </si>
-  <si>
-    <t>01-10-2026</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>29-07-2029</t>
-  </si>
-  <si>
-    <t>2000000</t>
-  </si>
-  <si>
-    <t>AQPPL2141K</t>
-  </si>
-  <si>
-    <t>SVR21015</t>
-  </si>
-  <si>
-    <t>SVR21011</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>9000</t>
-  </si>
-  <si>
-    <t>AQPPL2143K</t>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>2627CR710</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>2627CR714</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>2627CR715</t>
   </si>
 </sst>
 </file>
@@ -287,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,13 +311,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,7 +667,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,16 +691,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -682,93 +709,95 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -779,12 +808,15 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,12 +827,12 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1320,8 +1352,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="20.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="18.4285714285714" customWidth="1"/>
@@ -1334,180 +1366,246 @@
     <col min="14" max="14" width="18.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:15">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:20">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:20">
+      <c r="A2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="B2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J2">
+      <c r="C2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="10">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:20">
+      <c r="A3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" spans="1:20">
+      <c r="A4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="6" t="s">
+    <row r="5" s="3" customFormat="1" spans="1:20">
+      <c r="A5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3">
+      <c r="G5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
         <v>1</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="7" t="s">
+      <c r="M5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="S5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4" s="9">
-        <v>10000</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
